--- a/outputs/analysis/segment_conversion.xlsx
+++ b/outputs/analysis/segment_conversion.xlsx
@@ -96,13 +96,13 @@
     <t>Healthcare</t>
   </si>
   <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Management Consulting</t>
+  </si>
+  <si>
     <t>Marketing Agency</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Management Consulting</t>
   </si>
   <si>
     <t>Human Resources</t>
@@ -522,19 +522,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D2">
         <v>5107197.5</v>
       </c>
       <c r="E2">
-        <v>5751.348536036036</v>
+        <v>5764.331264108352</v>
       </c>
       <c r="F2">
-        <v>0.4673</v>
+        <v>0.4661</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -542,7 +542,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="C3">
         <v>487</v>
@@ -551,10 +551,10 @@
         <v>9398477.09</v>
       </c>
       <c r="E3">
-        <v>7218.492388632872</v>
+        <v>7240.737357473035</v>
       </c>
       <c r="F3">
-        <v>0.374</v>
+        <v>0.3752</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -606,7 +606,7 @@
         <v>1865</v>
       </c>
       <c r="C2">
-        <v>12144117.29</v>
+        <v>12114117.29</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -628,7 +628,7 @@
         <v>378</v>
       </c>
       <c r="C4">
-        <v>2386741.9</v>
+        <v>2366741.9</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -639,7 +639,7 @@
         <v>486</v>
       </c>
       <c r="C5">
-        <v>2306906.6</v>
+        <v>2286906.6</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -757,10 +757,10 @@
         <v>26</v>
       </c>
       <c r="B16">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16">
-        <v>136597.5</v>
+        <v>112275</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -768,10 +768,10 @@
         <v>27</v>
       </c>
       <c r="B17">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C17">
-        <v>112275</v>
+        <v>108268</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -779,10 +779,10 @@
         <v>28</v>
       </c>
       <c r="B18">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C18">
-        <v>108268</v>
+        <v>102404</v>
       </c>
     </row>
     <row r="19" spans="1:3">
